--- a/data/availability/projects/orascom-development/makadi-heights.xlsx
+++ b/data/availability/projects/orascom-development/makadi-heights.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Makadi Heights</t>
+          <t>Live inventory for makadi-heights</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,256 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>104</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>160</v>
+      </c>
+      <c r="F4" t="n">
+        <v>249</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>138</v>
+      </c>
+      <c r="F5" t="n">
+        <v>138</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>144</v>
+      </c>
+      <c r="F6" t="n">
+        <v>145</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>25.97</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
         </is>
       </c>
     </row>
@@ -557,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +877,2776 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AD/102-2-1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AD/105-2-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AD/106-2-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>120</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AD/107-2-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AD/108-2-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>19010000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AD/112-0-3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>104</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Garden: 58 sqm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>14964999</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AD/112-2-1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>16895000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AD/113-0-3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Garden: 62 sqm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>15020000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AD/113-2-1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>120</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>16895000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AD/115-0-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>95</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Garden: 52 sqm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>15160000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AD/115-0-3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>101</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Garden: 57 sqm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>15935000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AD/116-0-3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>104</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Garden: 58 sqm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>16474999</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AD/117-0-3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Garden: 64 sqm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>16280000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AD/118-0-2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>95</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Garden: 52 sqm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>15160000</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AD/118-0-3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>101</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Garden: 53 sqm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>15879999</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AD/93-0-3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>101</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Garden: 69 sqm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>14855000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AD/94-0-3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>104</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Garden: 64 sqm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>15044999</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AD/94-2-1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>120</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>16895000</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AD/95-0-3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>101</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Garden: 77 sqm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>14955000</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AD/96-0-1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>93</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Garden: 28 sqm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>14929999</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AD/96-2-1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>120</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>18255000</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AD/97-0-3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>104</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Garden: 67 sqm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>16365000</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AD/99-0-2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>95</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Garden: 61 sqm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>15295000</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AD/99-0-3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Aden Parks</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>101</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Garden: 73 sqm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>16180000</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SI/002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>192</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Garden: 324 sqm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>39600000</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SI/006</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>160</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Garden: 395 sqm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>31890000</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SI/007</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>192</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Garden: 350 sqm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>37620000</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SI/008</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>208</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Garden: 553 sqm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>47469999</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SI/009</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>160</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Garden: 337 sqm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>30235000</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SI/010</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>192</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Garden: 300 sqm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>36069999</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SI/011</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>160</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Garden: 336 sqm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SI/013</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>176</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Garden: 304 sqm</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>34545000</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SI/014A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>138</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Garden: 182 sqm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>22694999</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SI/016B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>144</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Garden: 179 sqm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>24709999</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SI/019</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>249</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Garden: 384 sqm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>49105001</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SI/020</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>192</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Garden: 301 sqm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>39380000</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SI/024A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>145</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Garden: 211 sqm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>25970000</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SI/027</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>176</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Garden: 293 sqm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>34720000</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SI/029</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>192</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Garden: 301 sqm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>36645000</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SI/031</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>176</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Garden: 335 sqm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>36050000</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SI/034A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>145</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Garden: 206 sqm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>25269999</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SI/034B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>144</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Garden: 205 sqm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>24740000</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SI/035A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>145</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Garden: 195 sqm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>24940000</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SI/036</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>192</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Garden: 300 sqm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>34975000</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SI/061</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>208</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Garden: 571 sqm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>51694999</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>makadi-heights</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SI/076</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Siyal</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>176</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Garden: 296 sqm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>34290000</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>10% downpayment over 7 years</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
